--- a/invoices.xlsx
+++ b/invoices.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:L16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1234,6 +1234,60 @@
         <v>2950</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>1043</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>10-02-2026 14:22</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>RITANSHA GUPTA</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>mahal, nagpur</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>09699276828</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Weighing machine</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2500.0</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>225</v>
+      </c>
+      <c r="K16" t="n">
+        <v>225</v>
+      </c>
+      <c r="L16" t="n">
+        <v>2950</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
